--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-qualityCertificate.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-qualityCertificate.xlsx
@@ -991,7 +991,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 10:30:31</t>
+          <t>2026-10-14 14:14:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-qualityCertificate.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-qualityCertificate.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -828,6 +828,23 @@
       <c r="C25" t="inlineStr">
         <is>
           <t>http://schema.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PREFIX</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>hrishapes</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>http://data.health-ri.nl/core/p2/</t>
         </is>
       </c>
     </row>
@@ -853,7 +870,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#aux-QualityCertificateShape</t>
+          <t>http://data.health-ri.nl/core/p2/aux-QualityCertificateShape</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -991,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 14:14:49</t>
+          <t>2026-10-14 14:30:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -1215,7 +1232,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hri:QualityCertificateShape</t>
+          <t>hrishapes:QualityCertificateShape</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1265,7 +1282,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#QualityCertificateShape</t>
+          <t>http://data.health-ri.nl/core/p2/QualityCertificateShape</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1684,12 +1701,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hri:QualityCertificateShape/oa:hasTarget</t>
+          <t>hrishapes:QualityCertificateShape#oa:hasTarget</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hri:QualityCertificateShape</t>
+          <t>hrishapes:QualityCertificateShape</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1744,12 +1761,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>hri:QualityCertificateShape/oa:hasBody</t>
+          <t>hrishapes:QualityCertificateShape#oa:hasBody</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>hri:QualityCertificateShape</t>
+          <t>hrishapes:QualityCertificateShape</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-qualityCertificate.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-qualityCertificate.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 14:30:39</t>
+          <t>2026-10-19 15:50:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-qualityCertificate.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-qualityCertificate.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-19 15:50:04</t>
+          <t>2026-10-26 13:15:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-qualityCertificate.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-qualityCertificate.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 13:15:51</t>
+          <t>2026-10-26 16:19:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-qualityCertificate.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-qualityCertificate.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 16:19:39</t>
+          <t>2026-10-27 15:44:14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-qualityCertificate.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-qualityCertificate.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 15:44:14</t>
+          <t>2026-10-28 09:50:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-qualityCertificate.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-qualityCertificate.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-28 09:50:42</t>
+          <t>2026-10-28 11:04:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
